--- a/ig/test-tabs-svs/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
+++ b/ig/test-tabs-svs/CodeSystem-tre-r347-activite-sanitaire-diverse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="997">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00.000+00:00</t>
+    <t>2026-06-29T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>461</t>
+    <t>478</t>
   </si>
   <si>
     <t>Code</t>
@@ -625,7 +625,7 @@
     <t>0371</t>
   </si>
   <si>
-    <t>structures de psychiatrie sans hébergement</t>
+    <t>structures de psychiatrie ambulatoire</t>
   </si>
   <si>
     <t>0372</t>
@@ -698,6 +698,108 @@
   </si>
   <si>
     <t>0821</t>
+  </si>
+  <si>
+    <t>861</t>
+  </si>
+  <si>
+    <t>Accueil familial thérapeutique</t>
+  </si>
+  <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>Appartement thérapeutique</t>
+  </si>
+  <si>
+    <t>863</t>
+  </si>
+  <si>
+    <t>Accueil permanent</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>Centre d'activités thérapeutiques et de temps de groupe</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>Centre de crise</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>Centre de soins post-aigus</t>
+  </si>
+  <si>
+    <t>867</t>
+  </si>
+  <si>
+    <t>Centre médico-psychologique</t>
+  </si>
+  <si>
+    <t>868</t>
+  </si>
+  <si>
+    <t>Hôpital de jour</t>
+  </si>
+  <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>Service médico-psychologique régional</t>
+  </si>
+  <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>Soins à domicile</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>Unité hospitalière spécialement aménagée</t>
+  </si>
+  <si>
+    <t>872</t>
+  </si>
+  <si>
+    <t>Unité pour malades difficiles</t>
+  </si>
+  <si>
+    <t>873</t>
+  </si>
+  <si>
+    <t>Unité sanitaire en milieu pénitentiaire</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>Hôpital de nuit</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>Centre de consultations</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>Unité d’hospitalisation complète</t>
+  </si>
+  <si>
+    <t>877</t>
+  </si>
+  <si>
+    <t>Centre d'accueil et de crise</t>
   </si>
   <si>
     <t>023</t>
@@ -3350,7 +3452,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D462"/>
+  <dimension ref="A1:D479"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5295,7 +5397,7 @@
         <v>364</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -5304,10 +5406,10 @@
         <v>70</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -5316,10 +5418,10 @@
         <v>70</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>153</v>
+        <v>369</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -5328,10 +5430,10 @@
         <v>70</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -5340,10 +5442,10 @@
         <v>70</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -5352,10 +5454,10 @@
         <v>70</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -5364,10 +5466,10 @@
         <v>70</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -5376,10 +5478,10 @@
         <v>70</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -5388,10 +5490,10 @@
         <v>70</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -5400,10 +5502,10 @@
         <v>70</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -5412,10 +5514,10 @@
         <v>70</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -5424,10 +5526,10 @@
         <v>70</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -5436,10 +5538,10 @@
         <v>70</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -5448,10 +5550,10 @@
         <v>70</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -5460,10 +5562,10 @@
         <v>70</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -5472,10 +5574,10 @@
         <v>70</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -5484,10 +5586,10 @@
         <v>70</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -5496,10 +5598,10 @@
         <v>70</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>397</v>
+        <v>159</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -5508,10 +5610,10 @@
         <v>70</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -5520,10 +5622,10 @@
         <v>70</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>401</v>
+        <v>153</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -5547,7 +5649,7 @@
         <v>404</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>161</v>
+        <v>405</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -5556,10 +5658,10 @@
         <v>70</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>163</v>
+        <v>407</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -5568,10 +5670,10 @@
         <v>70</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -5580,10 +5682,10 @@
         <v>70</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>169</v>
+        <v>411</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -5592,10 +5694,10 @@
         <v>70</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -5604,10 +5706,10 @@
         <v>70</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -5616,10 +5718,10 @@
         <v>70</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -5628,10 +5730,10 @@
         <v>70</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -5640,10 +5742,10 @@
         <v>70</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -5652,10 +5754,10 @@
         <v>70</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -5664,10 +5766,10 @@
         <v>70</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D193" s="2"/>
     </row>
@@ -5676,10 +5778,10 @@
         <v>70</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -5688,10 +5790,10 @@
         <v>70</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -5700,10 +5802,10 @@
         <v>70</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -5712,10 +5814,10 @@
         <v>70</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -5724,10 +5826,10 @@
         <v>70</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -5736,10 +5838,10 @@
         <v>70</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -5748,10 +5850,10 @@
         <v>70</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>436</v>
+        <v>161</v>
       </c>
       <c r="D200" s="2"/>
     </row>
@@ -5760,10 +5862,10 @@
         <v>70</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>438</v>
+        <v>163</v>
       </c>
       <c r="D201" s="2"/>
     </row>
@@ -5772,10 +5874,10 @@
         <v>70</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D202" s="2"/>
     </row>
@@ -5784,10 +5886,10 @@
         <v>70</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>442</v>
+        <v>169</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -5847,7 +5949,7 @@
         <v>451</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>88</v>
+        <v>452</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5856,10 +5958,10 @@
         <v>70</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5868,10 +5970,10 @@
         <v>70</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5880,10 +5982,10 @@
         <v>70</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5892,10 +5994,10 @@
         <v>70</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5904,10 +6006,10 @@
         <v>70</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5916,10 +6018,10 @@
         <v>70</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5928,10 +6030,10 @@
         <v>70</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5940,10 +6042,10 @@
         <v>70</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5952,10 +6054,10 @@
         <v>70</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5964,10 +6066,10 @@
         <v>70</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5976,10 +6078,10 @@
         <v>70</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5988,10 +6090,10 @@
         <v>70</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -6000,10 +6102,10 @@
         <v>70</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -6012,10 +6114,10 @@
         <v>70</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6024,10 +6126,10 @@
         <v>70</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6036,10 +6138,10 @@
         <v>70</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6048,10 +6150,10 @@
         <v>70</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>485</v>
+        <v>88</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -8379,7 +8481,7 @@
         <v>872</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>110</v>
+        <v>873</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8388,10 +8490,10 @@
         <v>70</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8400,10 +8502,10 @@
         <v>70</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8412,10 +8514,10 @@
         <v>70</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8424,10 +8526,10 @@
         <v>70</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8436,10 +8538,10 @@
         <v>70</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8448,10 +8550,10 @@
         <v>70</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D425" s="2"/>
     </row>
@@ -8460,10 +8562,10 @@
         <v>70</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D426" s="2"/>
     </row>
@@ -8472,10 +8574,10 @@
         <v>70</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -8484,10 +8586,10 @@
         <v>70</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8496,10 +8598,10 @@
         <v>70</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D429" s="2"/>
     </row>
@@ -8508,10 +8610,10 @@
         <v>70</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D430" s="2"/>
     </row>
@@ -8520,10 +8622,10 @@
         <v>70</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D431" s="2"/>
     </row>
@@ -8532,10 +8634,10 @@
         <v>70</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D432" s="2"/>
     </row>
@@ -8544,10 +8646,10 @@
         <v>70</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D433" s="2"/>
     </row>
@@ -8556,10 +8658,10 @@
         <v>70</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D434" s="2"/>
     </row>
@@ -8568,10 +8670,10 @@
         <v>70</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D435" s="2"/>
     </row>
@@ -8580,10 +8682,10 @@
         <v>70</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>906</v>
+        <v>110</v>
       </c>
       <c r="D436" s="2"/>
     </row>
@@ -8765,61 +8867,53 @@
       <c r="C451" t="s" s="2">
         <v>936</v>
       </c>
-      <c r="D451" t="s" s="2">
-        <v>937</v>
-      </c>
+      <c r="D451" s="2"/>
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B452" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="C452" t="s" s="2">
         <v>938</v>
       </c>
-      <c r="C452" t="s" s="2">
-        <v>939</v>
-      </c>
-      <c r="D452" t="s" s="2">
-        <v>940</v>
-      </c>
+      <c r="D452" s="2"/>
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>942</v>
-      </c>
-      <c r="D453" t="s" s="2">
-        <v>943</v>
-      </c>
+        <v>940</v>
+      </c>
+      <c r="D453" s="2"/>
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>945</v>
-      </c>
-      <c r="D454" t="s" s="2">
-        <v>946</v>
-      </c>
+        <v>942</v>
+      </c>
+      <c r="D454" s="2"/>
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
         <v>70</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D455" s="2"/>
     </row>
@@ -8828,10 +8922,10 @@
         <v>70</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="D456" s="2"/>
     </row>
@@ -8840,10 +8934,10 @@
         <v>70</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="D457" s="2"/>
     </row>
@@ -8852,10 +8946,10 @@
         <v>70</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="D458" s="2"/>
     </row>
@@ -8864,10 +8958,10 @@
         <v>70</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="D459" s="2"/>
     </row>
@@ -8876,10 +8970,10 @@
         <v>70</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="D460" s="2"/>
     </row>
@@ -8888,10 +8982,10 @@
         <v>70</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="D461" s="2"/>
     </row>
@@ -8900,12 +8994,224 @@
         <v>70</v>
       </c>
       <c r="B462" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="C462" t="s" s="2">
+        <v>958</v>
+      </c>
+      <c r="D462" s="2"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B463" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="C463" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="D463" s="2"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B464" t="s" s="2">
         <v>961</v>
       </c>
-      <c r="C462" t="s" s="2">
+      <c r="C464" t="s" s="2">
         <v>962</v>
       </c>
-      <c r="D462" s="2"/>
+      <c r="D464" s="2"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B465" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="C465" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="D465" s="2"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B466" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="C466" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="D466" s="2"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B467" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="C467" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="D467" s="2"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B468" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="C468" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="D468" t="s" s="2">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B469" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="C469" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="D469" t="s" s="2">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B470" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="C470" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="D470" t="s" s="2">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B471" t="s" s="2">
+        <v>978</v>
+      </c>
+      <c r="C471" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="D471" t="s" s="2">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B472" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="C472" t="s" s="2">
+        <v>982</v>
+      </c>
+      <c r="D472" s="2"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B473" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="C473" t="s" s="2">
+        <v>984</v>
+      </c>
+      <c r="D473" s="2"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B474" t="s" s="2">
+        <v>985</v>
+      </c>
+      <c r="C474" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="D474" s="2"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B475" t="s" s="2">
+        <v>987</v>
+      </c>
+      <c r="C475" t="s" s="2">
+        <v>988</v>
+      </c>
+      <c r="D475" s="2"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B476" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="C476" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="D476" s="2"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B477" t="s" s="2">
+        <v>991</v>
+      </c>
+      <c r="C477" t="s" s="2">
+        <v>992</v>
+      </c>
+      <c r="D477" s="2"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B478" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="C478" t="s" s="2">
+        <v>994</v>
+      </c>
+      <c r="D478" s="2"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B479" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="C479" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="D479" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
